--- a/data/output/random_test/0.1.timeslot_10.xlsx
+++ b/data/output/random_test/0.1.timeslot_10.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="325">
   <si>
     <t>name</t>
   </si>
@@ -80,10 +80,16 @@
     <t>q_mvar</t>
   </si>
   <si>
-    <t>const_z_percent</t>
-  </si>
-  <si>
-    <t>const_i_percent</t>
+    <t>const_z_p_percent</t>
+  </si>
+  <si>
+    <t>const_i_p_percent</t>
+  </si>
+  <si>
+    <t>const_z_q_percent</t>
+  </si>
+  <si>
+    <t>const_i_q_percent</t>
   </si>
   <si>
     <t>sn_mva</t>
@@ -224,6 +230,9 @@
     <t>tap_dependency_table</t>
   </si>
   <si>
+    <t>oltc</t>
+  </si>
+  <si>
     <t>6.6/0.1kV Transformer</t>
   </si>
   <si>
@@ -992,10 +1001,10 @@
     <t>f_hz</t>
   </si>
   <si>
-    <t>3.1.2</t>
-  </si>
-  <si>
-    <t>3.0.0</t>
+    <t>3.2.1</t>
+  </si>
+  <si>
+    <t>3.1.0</t>
   </si>
 </sst>
 </file>
@@ -1488,36 +1497,36 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -1526,27 +1535,27 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="F2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I2" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -1555,27 +1564,27 @@
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="I3" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B4" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C4">
         <v>125</v>
@@ -1584,27 +1593,27 @@
         <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="F4" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="I4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B5" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C5">
         <v>160</v>
@@ -1613,27 +1622,27 @@
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F5" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="I5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B6" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C6">
         <v>16</v>
@@ -1642,27 +1651,27 @@
         <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F6" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="I6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B7" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C7">
         <v>200</v>
@@ -1671,27 +1680,27 @@
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F7" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="I7" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B8" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C8">
         <v>20</v>
@@ -1700,27 +1709,27 @@
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="F8" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="I8" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B9" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C9">
         <v>25</v>
@@ -1729,27 +1738,27 @@
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F9" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="I9" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B10" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C10">
         <v>31.5</v>
@@ -1758,27 +1767,27 @@
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F10" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="I10" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B11" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C11">
         <v>40</v>
@@ -1787,27 +1796,27 @@
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F11" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="I11" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B12" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C12">
         <v>50</v>
@@ -1816,27 +1825,27 @@
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F12" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="I12" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B13" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C13">
         <v>6.3</v>
@@ -1845,27 +1854,27 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="F13" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="I13" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B14" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C14">
         <v>63</v>
@@ -1874,27 +1883,27 @@
         <v>0</v>
       </c>
       <c r="E14" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F14" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="I14" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B15" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C15">
         <v>80</v>
@@ -1903,33 +1912,33 @@
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F15" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
       <c r="H15" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="I15" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B16" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C16">
         <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1938,7 +1947,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -1949,16 +1958,16 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B17" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C17">
         <v>125</v>
       </c>
       <c r="D17" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1967,7 +1976,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -1978,16 +1987,16 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B18" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C18">
         <v>16</v>
       </c>
       <c r="D18" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1996,7 +2005,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -2007,16 +2016,16 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B19" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C19">
         <v>160</v>
       </c>
       <c r="D19" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -2025,7 +2034,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="H19">
         <v>0</v>
@@ -2036,16 +2045,16 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B20" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C20">
         <v>25</v>
       </c>
       <c r="D20" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -2054,7 +2063,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -2065,16 +2074,16 @@
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B21" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C21">
         <v>50</v>
       </c>
       <c r="D21" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -2083,7 +2092,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -2094,16 +2103,16 @@
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B22" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C22">
         <v>63</v>
       </c>
       <c r="D22" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -2112,7 +2121,7 @@
         <v>0</v>
       </c>
       <c r="G22" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -2123,16 +2132,16 @@
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B23" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C23">
         <v>80</v>
       </c>
       <c r="D23" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2141,7 +2150,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -2152,16 +2161,16 @@
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="1" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B24" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C24">
         <v>1000</v>
       </c>
       <c r="D24" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2170,7 +2179,7 @@
         <v>0</v>
       </c>
       <c r="G24" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -2181,16 +2190,16 @@
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="1" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B25" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C25">
         <v>200</v>
       </c>
       <c r="D25" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2199,7 +2208,7 @@
         <v>0</v>
       </c>
       <c r="G25" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -2210,16 +2219,16 @@
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B26" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C26">
         <v>224</v>
       </c>
       <c r="D26" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2228,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -2239,16 +2248,16 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B27" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C27">
         <v>250</v>
       </c>
       <c r="D27" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2257,7 +2266,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -2268,16 +2277,16 @@
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B28" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C28">
         <v>315</v>
       </c>
       <c r="D28" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2286,7 +2295,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -2297,16 +2306,16 @@
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B29" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C29">
         <v>355</v>
       </c>
       <c r="D29" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2315,7 +2324,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -2326,16 +2335,16 @@
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B30" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C30">
         <v>400</v>
       </c>
       <c r="D30" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2344,7 +2353,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="H30">
         <v>0</v>
@@ -2355,16 +2364,16 @@
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B31" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C31">
         <v>425</v>
       </c>
       <c r="D31" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2373,7 +2382,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="H31">
         <v>0</v>
@@ -2384,16 +2393,16 @@
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B32" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C32">
         <v>630</v>
       </c>
       <c r="D32" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2402,7 +2411,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="H32">
         <v>0</v>
@@ -2423,10 +2432,10 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>14</v>
@@ -2446,10 +2455,10 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>-0.002040791610943859</v>
+        <v>-0.002040805453470182</v>
       </c>
       <c r="E2">
-        <v>-0.0001236285118363051</v>
+        <v>-6.791110295384184E-05</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2457,10 +2466,10 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0.9997736170031448</v>
+        <v>0.9998065710534211</v>
       </c>
       <c r="C3">
-        <v>-0.051474080753397</v>
+        <v>-0.05179298197148764</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -2474,16 +2483,16 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0.9992053866791356</v>
+        <v>0.9992384073268146</v>
       </c>
       <c r="C4">
-        <v>-0.04772197088895663</v>
+        <v>-0.04978594180142182</v>
       </c>
       <c r="D4">
         <v>6.301565000000001E-05</v>
       </c>
       <c r="E4">
-        <v>1.753651475480455E-07</v>
+        <v>8.517307950130526E-06</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2491,16 +2500,16 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>0.9984775053441295</v>
+        <v>0.9985106305734784</v>
       </c>
       <c r="C5">
-        <v>-0.04260715725599052</v>
+        <v>-0.04740708680972251</v>
       </c>
       <c r="D5">
         <v>0.00029898205</v>
       </c>
       <c r="E5">
-        <v>4.170980165605057E-05</v>
+        <v>1.681937154776464E-05</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2508,16 +2517,16 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>0.9979389216269219</v>
+        <v>0.9979721151192054</v>
       </c>
       <c r="C6">
-        <v>-0.03902186253829389</v>
+        <v>-0.04560610202376558</v>
       </c>
       <c r="D6">
         <v>0.0006771176500000001</v>
       </c>
       <c r="E6">
-        <v>8.018149204813726E-05</v>
+        <v>4.101881410523285E-05</v>
       </c>
     </row>
   </sheetData>
@@ -2532,46 +2541,46 @@
   <sheetData>
     <row r="1" spans="1:15">
       <c r="B1" s="1" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -2579,46 +2588,46 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.00103888352016966</v>
+        <v>0.00103891523047107</v>
       </c>
       <c r="C2">
-        <v>0.0001219415446409035</v>
+        <v>6.629169528277564E-05</v>
       </c>
       <c r="D2">
-        <v>-0.001038285078147038</v>
+        <v>-0.001038322520844284</v>
       </c>
       <c r="E2">
-        <v>-0.0001219402321624233</v>
+        <v>-6.629039537635071E-05</v>
       </c>
       <c r="F2">
-        <v>5.984420226225889E-07</v>
+        <v>5.927096267857156E-07</v>
       </c>
       <c r="G2">
-        <v>1.312478480199964E-09</v>
+        <v>1.299906424932469E-09</v>
       </c>
       <c r="H2">
-        <v>0.006040541560684349</v>
+        <v>0.006011541177328704</v>
       </c>
       <c r="I2">
-        <v>0.006040541560684349</v>
+        <v>0.006011541177328704</v>
       </c>
       <c r="J2">
-        <v>0.006040541560684349</v>
+        <v>0.006011541177328704</v>
       </c>
       <c r="K2">
-        <v>0.9997736170031448</v>
+        <v>0.9998065710534211</v>
       </c>
       <c r="L2">
-        <v>-0.051474080753397</v>
+        <v>-0.05179298197148764</v>
       </c>
       <c r="M2">
-        <v>0.9992053866791356</v>
+        <v>0.9992384073268146</v>
       </c>
       <c r="N2">
-        <v>-0.04772197088895663</v>
+        <v>-0.04978594180142182</v>
       </c>
       <c r="O2">
-        <v>5.033784633903625</v>
+        <v>5.00961764777392</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -2626,46 +2635,46 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0.0009753294409030435</v>
+        <v>0.0009753574699283994</v>
       </c>
       <c r="C3">
-        <v>0.0001216073253172746</v>
+        <v>5.770644026327908E-05</v>
       </c>
       <c r="D3">
-        <v>-0.000974608100341339</v>
+        <v>-0.0009746446914125154</v>
       </c>
       <c r="E3">
-        <v>-0.000121605743302763</v>
+        <v>-5.770487702669494E-05</v>
       </c>
       <c r="F3">
-        <v>7.213405617044564E-07</v>
+        <v>7.127785158839639E-07</v>
       </c>
       <c r="G3">
-        <v>1.582014511592963E-09</v>
+        <v>1.563236584137804E-09</v>
       </c>
       <c r="H3">
-        <v>0.005679181201096444</v>
+        <v>0.005645375696169301</v>
       </c>
       <c r="I3">
-        <v>0.005679181201096443</v>
+        <v>0.0056453756961693</v>
       </c>
       <c r="J3">
-        <v>0.005679181201096444</v>
+        <v>0.005645375696169301</v>
       </c>
       <c r="K3">
-        <v>0.9992053866791356</v>
+        <v>0.9992384073268146</v>
       </c>
       <c r="L3">
-        <v>-0.04772197088895663</v>
+        <v>-0.04978594180142182</v>
       </c>
       <c r="M3">
-        <v>0.9984775053441295</v>
+        <v>0.9985106305734784</v>
       </c>
       <c r="N3">
-        <v>-0.04260715725599052</v>
+        <v>-0.04740708680972251</v>
       </c>
       <c r="O3">
-        <v>4.732651000913704</v>
+        <v>4.704479746807752</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -2673,46 +2682,46 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0.0006760894683793545</v>
+        <v>0.000676109930230754</v>
       </c>
       <c r="C4">
-        <v>7.989216680097437E-05</v>
+        <v>4.087246816685274E-05</v>
       </c>
       <c r="D4">
-        <v>-0.0006757197844733721</v>
+        <v>-0.0006757440071128583</v>
       </c>
       <c r="E4">
-        <v>-7.989135602540592E-05</v>
+        <v>-4.087166563929036E-05</v>
       </c>
       <c r="F4">
-        <v>3.696839059823655E-07</v>
+        <v>3.659231178957095E-07</v>
       </c>
       <c r="G4">
-        <v>8.107755684546875E-10</v>
+        <v>8.025275623828819E-10</v>
       </c>
       <c r="H4">
-        <v>0.003936556227489414</v>
+        <v>0.003916481782969365</v>
       </c>
       <c r="I4">
-        <v>0.003936556227489414</v>
+        <v>0.003916481782969366</v>
       </c>
       <c r="J4">
-        <v>0.003936556227489414</v>
+        <v>0.003916481782969366</v>
       </c>
       <c r="K4">
-        <v>0.9984775053441295</v>
+        <v>0.9985106305734784</v>
       </c>
       <c r="L4">
-        <v>-0.04260715725599052</v>
+        <v>-0.04740708680972251</v>
       </c>
       <c r="M4">
-        <v>0.9979389216269219</v>
+        <v>0.9979721151192054</v>
       </c>
       <c r="N4">
-        <v>-0.03902186253829389</v>
+        <v>-0.04560610202376558</v>
       </c>
       <c r="O4">
-        <v>3.280463522907846</v>
+        <v>3.263734819141138</v>
       </c>
     </row>
   </sheetData>
@@ -2727,43 +2736,43 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="B1" s="1" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>290</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -2771,28 +2780,28 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.002038970314462263</v>
+        <v>0.002039019638140127</v>
       </c>
       <c r="C2">
-        <v>0.0001234923978159497</v>
+        <v>6.779284019087228E-05</v>
       </c>
       <c r="D2">
-        <v>-0.001038983520008713</v>
+        <v>-0.001039000945930511</v>
       </c>
       <c r="E2">
-        <v>-0.0001219342500999407</v>
+        <v>-6.624089651072987E-05</v>
       </c>
       <c r="F2">
-        <v>0.0009999867944535501</v>
+        <v>0.001000018692209617</v>
       </c>
       <c r="G2">
-        <v>1.558147716008954E-06</v>
+        <v>1.55194368014241E-06</v>
       </c>
       <c r="H2">
-        <v>0.0001786904869897205</v>
+        <v>0.0001784665181096494</v>
       </c>
       <c r="I2">
-        <v>0.006041110193507741</v>
+        <v>0.00601201647582069</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -2801,13 +2810,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.9997736170031448</v>
+        <v>0.9998065710534211</v>
       </c>
       <c r="M2">
-        <v>-0.051474080753397</v>
+        <v>-0.05179298197148764</v>
       </c>
       <c r="N2">
-        <v>2.04270661514978</v>
+        <v>2.040146306984438</v>
       </c>
     </row>
   </sheetData>
@@ -2833,10 +2842,10 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.002040791610943859</v>
+        <v>0.002040805453470182</v>
       </c>
       <c r="C2">
-        <v>0.0001236285118363051</v>
+        <v>6.791110295384184E-05</v>
       </c>
     </row>
   </sheetData>
@@ -2865,7 +2874,7 @@
         <v>6.301565000000001E-05</v>
       </c>
       <c r="C2">
-        <v>1.753651475480455E-07</v>
+        <v>8.517307950130526E-06</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2876,7 +2885,7 @@
         <v>0.00029898205</v>
       </c>
       <c r="C3">
-        <v>4.170980165605057E-05</v>
+        <v>1.681937154776464E-05</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2887,7 +2896,7 @@
         <v>0.00067711765</v>
       </c>
       <c r="C4">
-        <v>8.018149204813727E-05</v>
+        <v>4.101881410523285E-05</v>
       </c>
     </row>
   </sheetData>
@@ -2897,18 +2906,18 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D99"/>
+  <dimension ref="A1:D102"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -2922,7 +2931,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2936,7 +2945,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2950,7 +2959,7 @@
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2964,7 +2973,7 @@
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2978,7 +2987,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2992,7 +3001,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -3000,13 +3009,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C8" t="s">
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -3014,13 +3023,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C9" t="s">
         <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -3028,13 +3037,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C10" t="s">
         <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -3042,13 +3051,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C11" t="s">
         <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -3056,13 +3065,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C12" t="s">
         <v>16</v>
       </c>
       <c r="D12" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -3070,13 +3079,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C13" t="s">
         <v>17</v>
       </c>
       <c r="D13" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -3084,13 +3093,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C14" t="s">
         <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -3098,13 +3107,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C15" t="s">
         <v>19</v>
       </c>
       <c r="D15" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -3112,13 +3121,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C16" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -3126,13 +3135,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C17" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D17" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -3140,13 +3149,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C18" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D18" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -3154,10 +3163,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C19" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D19" t="s">
         <v>313</v>
@@ -3168,13 +3177,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C20" t="s">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D20" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -3182,13 +3191,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C21" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D21" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -3196,13 +3205,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C22" t="s">
         <v>26</v>
       </c>
       <c r="D22" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -3210,13 +3219,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C23" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="D23" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -3224,13 +3233,13 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D24" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -3238,13 +3247,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C25" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -3252,13 +3261,13 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C26" t="s">
         <v>29</v>
       </c>
       <c r="D26" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -3266,10 +3275,10 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C27" t="s">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D27" t="s">
         <v>313</v>
@@ -3280,7 +3289,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C28" t="s">
         <v>31</v>
@@ -3294,13 +3303,13 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C29" t="s">
         <v>32</v>
       </c>
       <c r="D29" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -3308,13 +3317,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C30" t="s">
         <v>33</v>
       </c>
       <c r="D30" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -3322,13 +3331,13 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C31" t="s">
         <v>34</v>
       </c>
       <c r="D31" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -3336,13 +3345,13 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C32" t="s">
         <v>35</v>
       </c>
       <c r="D32" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -3350,13 +3359,13 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C33" t="s">
         <v>36</v>
       </c>
       <c r="D33" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -3364,13 +3373,13 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C34" t="s">
         <v>37</v>
       </c>
       <c r="D34" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -3378,13 +3387,13 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C35" t="s">
         <v>38</v>
       </c>
       <c r="D35" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -3392,13 +3401,13 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C36" t="s">
         <v>39</v>
       </c>
       <c r="D36" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -3406,13 +3415,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C37" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="D37" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -3420,13 +3429,13 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C38" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="D38" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -3434,13 +3443,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C39" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D39" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -3448,13 +3457,13 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C40" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D40" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -3462,13 +3471,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C41" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="D41" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -3476,10 +3485,10 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C42" t="s">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="D42" t="s">
         <v>313</v>
@@ -3490,10 +3499,10 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C43" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="D43" t="s">
         <v>313</v>
@@ -3504,13 +3513,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C44" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="D44" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -3518,13 +3527,13 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C45" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D45" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -3532,13 +3541,13 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C46" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="D46" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -3546,13 +3555,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C47" t="s">
         <v>49</v>
       </c>
       <c r="D47" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -3560,13 +3569,13 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C48" t="s">
         <v>50</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -3574,13 +3583,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C49" t="s">
         <v>51</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -3588,13 +3597,13 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C50" t="s">
         <v>52</v>
       </c>
       <c r="D50" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -3602,13 +3611,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C51" t="s">
         <v>53</v>
       </c>
       <c r="D51" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -3616,13 +3625,13 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C52" t="s">
         <v>54</v>
       </c>
       <c r="D52" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -3630,13 +3639,13 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C53" t="s">
         <v>55</v>
       </c>
       <c r="D53" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -3644,13 +3653,13 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C54" t="s">
         <v>56</v>
       </c>
       <c r="D54" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -3658,13 +3667,13 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C55" t="s">
         <v>57</v>
       </c>
       <c r="D55" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -3672,13 +3681,13 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C56" t="s">
         <v>58</v>
       </c>
       <c r="D56" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -3686,13 +3695,13 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C57" t="s">
         <v>59</v>
       </c>
       <c r="D57" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -3700,13 +3709,13 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C58" t="s">
         <v>60</v>
       </c>
       <c r="D58" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -3714,13 +3723,13 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C59" t="s">
         <v>61</v>
       </c>
       <c r="D59" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -3728,7 +3737,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C60" t="s">
         <v>62</v>
@@ -3742,13 +3751,13 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C61" t="s">
         <v>63</v>
       </c>
       <c r="D61" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -3756,13 +3765,13 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C62" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="D62" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -3770,13 +3779,13 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C63" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="D63" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -3784,13 +3793,13 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C64" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="D64" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -3798,13 +3807,13 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C65" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D65" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -3812,13 +3821,13 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C66" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="D66" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -3826,13 +3835,13 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C67" t="s">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="D67" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -3840,13 +3849,13 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C68" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D68" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -3854,13 +3863,13 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C69" t="s">
-        <v>274</v>
+        <v>27</v>
       </c>
       <c r="D69" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -3868,13 +3877,13 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C70" t="s">
-        <v>275</v>
+        <v>14</v>
       </c>
       <c r="D70" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -3882,13 +3891,13 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C71" t="s">
-        <v>276</v>
+        <v>15</v>
       </c>
       <c r="D71" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -3896,13 +3905,13 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C72" t="s">
         <v>277</v>
       </c>
       <c r="D72" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -3910,13 +3919,13 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C73" t="s">
         <v>278</v>
       </c>
       <c r="D73" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -3924,13 +3933,13 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C74" t="s">
         <v>279</v>
       </c>
       <c r="D74" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -3938,13 +3947,13 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C75" t="s">
         <v>280</v>
       </c>
       <c r="D75" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3952,13 +3961,13 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C76" t="s">
         <v>281</v>
       </c>
       <c r="D76" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3966,13 +3975,13 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C77" t="s">
         <v>282</v>
       </c>
       <c r="D77" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3980,13 +3989,13 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C78" t="s">
         <v>283</v>
       </c>
       <c r="D78" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3994,13 +4003,13 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C79" t="s">
         <v>284</v>
       </c>
       <c r="D79" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -4008,13 +4017,13 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C80" t="s">
         <v>285</v>
       </c>
       <c r="D80" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -4022,13 +4031,13 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C81" t="s">
         <v>286</v>
       </c>
       <c r="D81" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -4036,13 +4045,13 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C82" t="s">
         <v>287</v>
       </c>
       <c r="D82" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -4050,13 +4059,13 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C83" t="s">
         <v>288</v>
       </c>
       <c r="D83" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -4064,13 +4073,13 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C84" t="s">
         <v>289</v>
       </c>
       <c r="D84" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -4078,13 +4087,13 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C85" t="s">
         <v>290</v>
       </c>
       <c r="D85" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -4092,13 +4101,13 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C86" t="s">
         <v>291</v>
       </c>
       <c r="D86" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -4106,13 +4115,13 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C87" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="D87" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -4120,13 +4129,13 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C88" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="D88" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -4134,13 +4143,13 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C89" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D89" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -4148,13 +4157,13 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C90" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="D90" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -4162,13 +4171,13 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C91" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="D91" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -4176,13 +4185,13 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C92" t="s">
         <v>295</v>
       </c>
       <c r="D92" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -4190,13 +4199,13 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C93" t="s">
         <v>296</v>
       </c>
       <c r="D93" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -4204,13 +4213,13 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C94" t="s">
         <v>297</v>
       </c>
       <c r="D94" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -4218,13 +4227,13 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C95" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="D95" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -4232,13 +4241,13 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C96" t="s">
-        <v>14</v>
+        <v>299</v>
       </c>
       <c r="D96" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -4246,13 +4255,13 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C97" t="s">
-        <v>15</v>
+        <v>300</v>
       </c>
       <c r="D97" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -4260,13 +4269,13 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C98" t="s">
-        <v>14</v>
+        <v>290</v>
       </c>
       <c r="D98" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -4274,13 +4283,55 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C99" t="s">
+        <v>14</v>
+      </c>
+      <c r="D99" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" s="1">
+        <v>98</v>
+      </c>
+      <c r="B100" t="s">
+        <v>311</v>
+      </c>
+      <c r="C100" t="s">
         <v>15</v>
       </c>
-      <c r="D99" t="s">
-        <v>311</v>
+      <c r="D100" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" s="1">
+        <v>99</v>
+      </c>
+      <c r="B101" t="s">
+        <v>312</v>
+      </c>
+      <c r="C101" t="s">
+        <v>14</v>
+      </c>
+      <c r="D101" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" s="1">
+        <v>100</v>
+      </c>
+      <c r="B102" t="s">
+        <v>312</v>
+      </c>
+      <c r="C102" t="s">
+        <v>15</v>
+      </c>
+      <c r="D102" t="s">
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -4295,25 +4346,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -4321,10 +4372,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C2" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D2" t="b">
         <v>1</v>
@@ -4346,10 +4397,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4375,18 +4426,24 @@
         <v>19</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:13">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C2">
         <v>2</v>
@@ -4395,7 +4452,7 @@
         <v>6.301565000000001E-05</v>
       </c>
       <c r="E2">
-        <v>1.753651475480455E-07</v>
+        <v>8.517307950130526E-06</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -4403,22 +4460,28 @@
       <c r="G2">
         <v>0</v>
       </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
       <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="K2">
         <v>1</v>
       </c>
-      <c r="J2" t="b">
+      <c r="L2" t="b">
         <v>1</v>
       </c>
-      <c r="K2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="M2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -4427,7 +4490,7 @@
         <v>0.00029898205</v>
       </c>
       <c r="E3">
-        <v>4.170980165605057E-05</v>
+        <v>1.681937154776464E-05</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -4435,22 +4498,28 @@
       <c r="G3">
         <v>0</v>
       </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
       <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="K3">
         <v>1</v>
       </c>
-      <c r="J3" t="b">
+      <c r="L3" t="b">
         <v>1</v>
       </c>
-      <c r="K3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="M3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -4459,7 +4528,7 @@
         <v>0.00067711765</v>
       </c>
       <c r="E4">
-        <v>8.018149204813727E-05</v>
+        <v>4.101881410523285E-05</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -4467,14 +4536,20 @@
       <c r="G4">
         <v>0</v>
       </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
       <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="K4">
         <v>1</v>
       </c>
-      <c r="J4" t="b">
+      <c r="L4" t="b">
         <v>1</v>
       </c>
-      <c r="K4" t="s">
-        <v>23</v>
+      <c r="M4" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -4495,19 +4570,19 @@
         <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -4515,7 +4590,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -4551,37 +4626,37 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>2</v>
@@ -4598,10 +4673,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -4637,7 +4712,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -4645,10 +4720,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -4684,7 +4759,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -4692,10 +4767,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -4731,7 +4806,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -4741,92 +4816,95 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:AA2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:26">
+      <c r="AA1" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -4869,6 +4947,9 @@
       </c>
       <c r="Z2" t="b">
         <v>1</v>
+      </c>
+      <c r="AA2" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4883,33 +4964,33 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B2">
         <v>210</v>
@@ -4924,7 +5005,7 @@
         <v>0.142</v>
       </c>
       <c r="F2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G2">
         <v>50</v>
@@ -4933,12 +5014,12 @@
         <v>0.00403</v>
       </c>
       <c r="I2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B3">
         <v>264</v>
@@ -4953,7 +5034,7 @@
         <v>0.242</v>
       </c>
       <c r="F3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G3">
         <v>120</v>
@@ -4962,12 +5043,12 @@
         <v>0.00403</v>
       </c>
       <c r="I3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B4">
         <v>261</v>
@@ -4982,7 +5063,7 @@
         <v>0.27</v>
       </c>
       <c r="F4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G4">
         <v>150</v>
@@ -4991,12 +5072,12 @@
         <v>0.00403</v>
       </c>
       <c r="I4" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B5">
         <v>216</v>
@@ -5011,7 +5092,7 @@
         <v>0.252</v>
       </c>
       <c r="F5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G5">
         <v>95</v>
@@ -5020,12 +5101,12 @@
         <v>0.00403</v>
       </c>
       <c r="I5" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B6">
         <v>273</v>
@@ -5040,7 +5121,7 @@
         <v>0.362</v>
       </c>
       <c r="F6" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G6">
         <v>185</v>
@@ -5049,12 +5130,12 @@
         <v>0.00403</v>
       </c>
       <c r="I6" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B7">
         <v>304</v>
@@ -5069,7 +5150,7 @@
         <v>0.421</v>
       </c>
       <c r="F7" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G7">
         <v>240</v>
@@ -5078,12 +5159,12 @@
         <v>0.00403</v>
       </c>
       <c r="I7" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B8">
         <v>315</v>
@@ -5098,7 +5179,7 @@
         <v>0.249</v>
       </c>
       <c r="F8" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G8">
         <v>95</v>
@@ -5107,12 +5188,12 @@
         <v>0.00403</v>
       </c>
       <c r="I8" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B9">
         <v>406</v>
@@ -5127,7 +5208,7 @@
         <v>0.358</v>
       </c>
       <c r="F9" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G9">
         <v>185</v>
@@ -5136,12 +5217,12 @@
         <v>0.00403</v>
       </c>
       <c r="I9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B10">
         <v>456</v>
@@ -5156,7 +5237,7 @@
         <v>0.416</v>
       </c>
       <c r="F10" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G10">
         <v>240</v>
@@ -5165,12 +5246,12 @@
         <v>0.00403</v>
       </c>
       <c r="I10" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B11">
         <v>250</v>
@@ -5185,7 +5266,7 @@
         <v>0.319</v>
       </c>
       <c r="F11" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G11">
         <v>150</v>
@@ -5194,12 +5275,12 @@
         <v>0.00403</v>
       </c>
       <c r="I11" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B12">
         <v>230</v>
@@ -5214,7 +5295,7 @@
         <v>0.283</v>
       </c>
       <c r="F12" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G12">
         <v>120</v>
@@ -5223,12 +5304,12 @@
         <v>0.00403</v>
       </c>
       <c r="I12" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B13">
         <v>190</v>
@@ -5243,7 +5324,7 @@
         <v>0.22</v>
       </c>
       <c r="F13" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G13">
         <v>70</v>
@@ -5252,12 +5333,12 @@
         <v>0.00403</v>
       </c>
       <c r="I13" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B14">
         <v>360</v>
@@ -5272,7 +5353,7 @@
         <v>0.315</v>
       </c>
       <c r="F14" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G14">
         <v>150</v>
@@ -5281,12 +5362,12 @@
         <v>0.00403</v>
       </c>
       <c r="I14" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B15">
         <v>340</v>
@@ -5301,7 +5382,7 @@
         <v>0.28</v>
       </c>
       <c r="F15" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G15">
         <v>120</v>
@@ -5310,12 +5391,12 @@
         <v>0.00403</v>
       </c>
       <c r="I15" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B16">
         <v>280</v>
@@ -5330,7 +5411,7 @@
         <v>0.217</v>
       </c>
       <c r="F16" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G16">
         <v>70</v>
@@ -5339,12 +5420,12 @@
         <v>0.00403</v>
       </c>
       <c r="I16" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B17">
         <v>112</v>
@@ -5359,7 +5440,7 @@
         <v>0.366</v>
       </c>
       <c r="F17" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G17">
         <v>120</v>
@@ -5368,12 +5449,12 @@
         <v>0.00393</v>
       </c>
       <c r="I17" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B18">
         <v>125</v>
@@ -5388,7 +5469,7 @@
         <v>0.457</v>
       </c>
       <c r="F18" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G18">
         <v>185</v>
@@ -5397,12 +5478,12 @@
         <v>0.00393</v>
       </c>
       <c r="I18" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B19">
         <v>135</v>
@@ -5417,7 +5498,7 @@
         <v>0.526</v>
       </c>
       <c r="F19" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G19">
         <v>240</v>
@@ -5426,12 +5507,12 @@
         <v>0.00393</v>
       </c>
       <c r="I19" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B20">
         <v>144</v>
@@ -5446,7 +5527,7 @@
         <v>0.588</v>
       </c>
       <c r="F20" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G20">
         <v>300</v>
@@ -5455,12 +5536,12 @@
         <v>0.00393</v>
       </c>
       <c r="I20" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B21">
         <v>11</v>
@@ -5475,7 +5556,7 @@
         <v>0.105</v>
       </c>
       <c r="F21" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G21">
         <v>16</v>
@@ -5484,12 +5565,12 @@
         <v>0.00403</v>
       </c>
       <c r="I21" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B22">
         <v>11.25</v>
@@ -5504,7 +5585,7 @@
         <v>0.14</v>
       </c>
       <c r="F22" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G22">
         <v>24</v>
@@ -5513,12 +5594,12 @@
         <v>0.00403</v>
       </c>
       <c r="I22" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B23">
         <v>12.2</v>
@@ -5533,7 +5614,7 @@
         <v>0.21</v>
       </c>
       <c r="F23" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G23">
         <v>48</v>
@@ -5542,12 +5623,12 @@
         <v>0.00403</v>
       </c>
       <c r="I23" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B24">
         <v>13.2</v>
@@ -5562,7 +5643,7 @@
         <v>0.35</v>
       </c>
       <c r="F24" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G24">
         <v>94</v>
@@ -5571,12 +5652,12 @@
         <v>0.00403</v>
       </c>
       <c r="I24" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B25">
         <v>9.699999999999999</v>
@@ -5591,7 +5672,7 @@
         <v>0.17</v>
       </c>
       <c r="F25" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G25">
         <v>34</v>
@@ -5600,12 +5681,12 @@
         <v>0.00403</v>
       </c>
       <c r="I25" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B26">
         <v>10.1</v>
@@ -5620,7 +5701,7 @@
         <v>0.21</v>
       </c>
       <c r="F26" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G26">
         <v>48</v>
@@ -5629,12 +5710,12 @@
         <v>0.00403</v>
       </c>
       <c r="I26" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B27">
         <v>10.4</v>
@@ -5649,7 +5730,7 @@
         <v>0.29</v>
       </c>
       <c r="F27" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G27">
         <v>70</v>
@@ -5658,12 +5739,12 @@
         <v>0.00403</v>
       </c>
       <c r="I27" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B28">
         <v>10.75</v>
@@ -5678,7 +5759,7 @@
         <v>0.35</v>
       </c>
       <c r="F28" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G28">
         <v>94</v>
@@ -5687,12 +5768,12 @@
         <v>0.00403</v>
       </c>
       <c r="I28" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B29">
         <v>11.1</v>
@@ -5707,7 +5788,7 @@
         <v>0.41</v>
       </c>
       <c r="F29" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G29">
         <v>122</v>
@@ -5716,12 +5797,12 @@
         <v>0.00403</v>
       </c>
       <c r="I29" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B30">
         <v>11.25</v>
@@ -5736,7 +5817,7 @@
         <v>0.47</v>
       </c>
       <c r="F30" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G30">
         <v>149</v>
@@ -5745,12 +5826,12 @@
         <v>0.00403</v>
       </c>
       <c r="I30" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B31">
         <v>9.15</v>
@@ -5765,7 +5846,7 @@
         <v>0.17</v>
       </c>
       <c r="F31" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G31">
         <v>34</v>
@@ -5774,12 +5855,12 @@
         <v>0.00403</v>
       </c>
       <c r="I31" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B32">
         <v>9.5</v>
@@ -5794,7 +5875,7 @@
         <v>0.21</v>
       </c>
       <c r="F32" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G32">
         <v>48</v>
@@ -5803,12 +5884,12 @@
         <v>0.00403</v>
       </c>
       <c r="I32" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B33">
         <v>9.699999999999999</v>
@@ -5823,7 +5904,7 @@
         <v>0.29</v>
       </c>
       <c r="F33" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G33">
         <v>70</v>
@@ -5832,12 +5913,12 @@
         <v>0.00403</v>
       </c>
       <c r="I33" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B34">
         <v>10</v>
@@ -5852,7 +5933,7 @@
         <v>0.35</v>
       </c>
       <c r="F34" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G34">
         <v>94</v>
@@ -5861,12 +5942,12 @@
         <v>0.00403</v>
       </c>
       <c r="I34" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B35">
         <v>10.3</v>
@@ -5881,7 +5962,7 @@
         <v>0.41</v>
       </c>
       <c r="F35" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G35">
         <v>122</v>
@@ -5890,12 +5971,12 @@
         <v>0.00403</v>
       </c>
       <c r="I35" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B36">
         <v>10.5</v>
@@ -5910,7 +5991,7 @@
         <v>0.47</v>
       </c>
       <c r="F36" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G36">
         <v>149</v>
@@ -5919,12 +6000,12 @@
         <v>0.00403</v>
       </c>
       <c r="I36" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B37">
         <v>10.75</v>
@@ -5939,7 +6020,7 @@
         <v>0.535</v>
       </c>
       <c r="F37" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G37">
         <v>184</v>
@@ -5948,12 +6029,12 @@
         <v>0.00403</v>
       </c>
       <c r="I37" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B38">
         <v>11</v>
@@ -5968,7 +6049,7 @@
         <v>0.645</v>
       </c>
       <c r="F38" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G38">
         <v>243</v>
@@ -5977,12 +6058,12 @@
         <v>0.00403</v>
       </c>
       <c r="I38" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B39">
         <v>8</v>
@@ -5997,7 +6078,7 @@
         <v>0.21</v>
       </c>
       <c r="F39" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G39">
         <v>48</v>
@@ -6006,12 +6087,12 @@
         <v>0.00403</v>
       </c>
       <c r="I39" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B40">
         <v>8.4</v>
@@ -6026,7 +6107,7 @@
         <v>0.29</v>
       </c>
       <c r="F40" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G40">
         <v>70</v>
@@ -6035,12 +6116,12 @@
         <v>0.00403</v>
       </c>
       <c r="I40" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B41">
         <v>8.65</v>
@@ -6055,7 +6136,7 @@
         <v>0.35</v>
       </c>
       <c r="F41" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G41">
         <v>94</v>
@@ -6064,12 +6145,12 @@
         <v>0.00403</v>
       </c>
       <c r="I41" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B42">
         <v>8.5</v>
@@ -6084,7 +6165,7 @@
         <v>0.41</v>
       </c>
       <c r="F42" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G42">
         <v>122</v>
@@ -6093,12 +6174,12 @@
         <v>0.00403</v>
       </c>
       <c r="I42" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B43">
         <v>8.75</v>
@@ -6113,7 +6194,7 @@
         <v>0.47</v>
       </c>
       <c r="F43" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G43">
         <v>149</v>
@@ -6122,12 +6203,12 @@
         <v>0.00403</v>
       </c>
       <c r="I43" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B44">
         <v>8.800000000000001</v>
@@ -6142,7 +6223,7 @@
         <v>0.535</v>
       </c>
       <c r="F44" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G44">
         <v>184</v>
@@ -6151,12 +6232,12 @@
         <v>0.00403</v>
       </c>
       <c r="I44" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B45">
         <v>9</v>
@@ -6171,7 +6252,7 @@
         <v>0.645</v>
       </c>
       <c r="F45" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G45">
         <v>243</v>
@@ -6180,12 +6261,12 @@
         <v>0.00403</v>
       </c>
       <c r="I45" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B46">
         <v>9.199999999999999</v>
@@ -6200,7 +6281,7 @@
         <v>0.74</v>
       </c>
       <c r="F46" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G46">
         <v>305</v>
@@ -6209,12 +6290,12 @@
         <v>0.00403</v>
       </c>
       <c r="I46" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B47">
         <v>9.75</v>
@@ -6229,7 +6310,7 @@
         <v>0.96</v>
       </c>
       <c r="F47" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G47">
         <v>490</v>
@@ -6238,12 +6319,12 @@
         <v>0.00403</v>
       </c>
       <c r="I47" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B48">
         <v>9.949999999999999</v>
@@ -6258,7 +6339,7 @@
         <v>1.15</v>
       </c>
       <c r="F48" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G48">
         <v>679</v>
@@ -6267,12 +6348,12 @@
         <v>0.00403</v>
       </c>
       <c r="I48" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B49">
         <v>10</v>
@@ -6287,7 +6368,7 @@
         <v>0.96</v>
       </c>
       <c r="F49" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G49">
         <v>490</v>
@@ -6296,12 +6377,12 @@
         <v>0.00403</v>
       </c>
       <c r="I49" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="50" spans="1:9">
       <c r="A50" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B50">
         <v>11.7</v>
@@ -6316,7 +6397,7 @@
         <v>1.15</v>
       </c>
       <c r="F50" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G50">
         <v>679</v>
@@ -6325,12 +6406,12 @@
         <v>0.00403</v>
       </c>
       <c r="I50" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="51" spans="1:9">
       <c r="A51" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B51">
         <v>11</v>
@@ -6345,7 +6426,7 @@
         <v>0.96</v>
       </c>
       <c r="F51" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G51">
         <v>490</v>
@@ -6354,12 +6435,12 @@
         <v>0.00403</v>
       </c>
       <c r="I51" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="52" spans="1:9">
       <c r="A52" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B52">
         <v>14.6</v>
@@ -6374,7 +6455,7 @@
         <v>1.15</v>
       </c>
       <c r="F52" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G52">
         <v>679</v>
@@ -6383,12 +6464,12 @@
         <v>0.00403</v>
       </c>
       <c r="I52" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="53" spans="1:9">
       <c r="A53" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -6415,24 +6496,24 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B2">
         <v>0.193</v>
@@ -6441,7 +6522,7 @@
         <v>0.404</v>
       </c>
       <c r="D2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E2">
         <v>95</v>
@@ -6452,7 +6533,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B3">
         <v>0.047</v>
@@ -6461,7 +6542,7 @@
         <v>0.922</v>
       </c>
       <c r="D3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E3">
         <v>400</v>
@@ -6472,7 +6553,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B4">
         <v>0.0151</v>
@@ -6481,7 +6562,7 @@
         <v>1.791</v>
       </c>
       <c r="D4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E4">
         <v>1200</v>
@@ -6492,7 +6573,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B5">
         <v>0.0073</v>
@@ -6501,7 +6582,7 @@
         <v>2.678</v>
       </c>
       <c r="D5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E5">
         <v>2400</v>
@@ -6512,7 +6593,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B6">
         <v>0.32</v>
@@ -6521,7 +6602,7 @@
         <v>0.31</v>
       </c>
       <c r="D6" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E6">
         <v>95</v>
@@ -6532,7 +6613,7 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B7">
         <v>0.07779999999999999</v>
@@ -6541,7 +6622,7 @@
         <v>0.705</v>
       </c>
       <c r="D7" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E7">
         <v>400</v>
@@ -6552,7 +6633,7 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B8">
         <v>0.0247</v>
@@ -6561,7 +6642,7 @@
         <v>1.371</v>
       </c>
       <c r="D8" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E8">
         <v>1200</v>
@@ -6572,7 +6653,7 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B9">
         <v>0.0121</v>
@@ -6581,7 +6662,7 @@
         <v>2.066</v>
       </c>
       <c r="D9" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E9">
         <v>2400</v>
@@ -6602,60 +6683,60 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="B1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B2">
         <v>0.06</v>
@@ -6682,10 +6763,10 @@
         <v>0</v>
       </c>
       <c r="J2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="K2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -6703,7 +6784,7 @@
         <v>1.5</v>
       </c>
       <c r="Q2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="R2" t="b">
         <v>0</v>
@@ -6711,7 +6792,7 @@
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B3">
         <v>0.06</v>
@@ -6738,10 +6819,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="K3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -6759,7 +6840,7 @@
         <v>1.5</v>
       </c>
       <c r="Q3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="R3" t="b">
         <v>0</v>
@@ -6767,7 +6848,7 @@
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B4">
         <v>0.04</v>
@@ -6794,10 +6875,10 @@
         <v>150</v>
       </c>
       <c r="J4" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="K4" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -6815,7 +6896,7 @@
         <v>1.5</v>
       </c>
       <c r="Q4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
@@ -6823,7 +6904,7 @@
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B5">
         <v>0.05</v>
@@ -6850,10 +6931,10 @@
         <v>150</v>
       </c>
       <c r="J5" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="K5" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -6871,7 +6952,7 @@
         <v>1.5</v>
       </c>
       <c r="Q5" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="R5" t="b">
         <v>0</v>
@@ -6879,7 +6960,7 @@
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B6">
         <v>0.07000000000000001</v>
@@ -6906,10 +6987,10 @@
         <v>150</v>
       </c>
       <c r="J6" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="K6" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -6927,7 +7008,7 @@
         <v>1.5</v>
       </c>
       <c r="Q6" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="R6" t="b">
         <v>0</v>
@@ -6935,7 +7016,7 @@
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B7">
         <v>0.04</v>
@@ -6962,10 +7043,10 @@
         <v>150</v>
       </c>
       <c r="J7" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="K7" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -6983,7 +7064,7 @@
         <v>1.5</v>
       </c>
       <c r="Q7" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
@@ -6991,7 +7072,7 @@
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B8">
         <v>0.05</v>
@@ -7018,10 +7099,10 @@
         <v>150</v>
       </c>
       <c r="J8" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="K8" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -7039,7 +7120,7 @@
         <v>1.5</v>
       </c>
       <c r="Q8" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="R8" t="b">
         <v>0</v>
@@ -7047,7 +7128,7 @@
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B9">
         <v>0.07000000000000001</v>
@@ -7074,10 +7155,10 @@
         <v>150</v>
       </c>
       <c r="J9" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="K9" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -7095,7 +7176,7 @@
         <v>1.5</v>
       </c>
       <c r="Q9" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="R9" t="b">
         <v>0</v>
@@ -7103,7 +7184,7 @@
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B10">
         <v>0.32</v>
@@ -7130,10 +7211,10 @@
         <v>150</v>
       </c>
       <c r="J10" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="K10" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -7151,7 +7232,7 @@
         <v>2.5</v>
       </c>
       <c r="Q10" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="R10" t="b">
         <v>0</v>
@@ -7159,7 +7240,7 @@
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B11">
         <v>0.3375</v>
@@ -7186,10 +7267,10 @@
         <v>150</v>
       </c>
       <c r="J11" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="K11" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -7207,7 +7288,7 @@
         <v>2.5</v>
       </c>
       <c r="Q11" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="R11" t="b">
         <v>0</v>
@@ -7215,7 +7296,7 @@
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B12">
         <v>0.2619</v>
@@ -7242,10 +7323,10 @@
         <v>150</v>
       </c>
       <c r="J12" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="K12" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -7263,7 +7344,7 @@
         <v>2.5</v>
       </c>
       <c r="Q12" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="R12" t="b">
         <v>0</v>
@@ -7271,7 +7352,7 @@
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B13">
         <v>0.24</v>
@@ -7298,10 +7379,10 @@
         <v>150</v>
       </c>
       <c r="J13" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="K13" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -7319,7 +7400,7 @@
         <v>2.5</v>
       </c>
       <c r="Q13" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="R13" t="b">
         <v>0</v>
@@ -7327,7 +7408,7 @@
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B14">
         <v>0.2375</v>
@@ -7354,10 +7435,10 @@
         <v>150</v>
       </c>
       <c r="J14" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="K14" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -7375,7 +7456,7 @@
         <v>2.5</v>
       </c>
       <c r="Q14" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="R14" t="b">
         <v>0</v>
@@ -7383,7 +7464,7 @@
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B15">
         <v>0.1873</v>
@@ -7410,10 +7491,10 @@
         <v>150</v>
       </c>
       <c r="J15" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="K15" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -7431,7 +7512,7 @@
         <v>2.5</v>
       </c>
       <c r="Q15" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="R15" t="b">
         <v>0</v>
@@ -7449,81 +7530,81 @@
   <sheetData>
     <row r="1" spans="1:25">
       <c r="B1" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:25">
       <c r="A2" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B2">
         <v>63</v>
@@ -7574,10 +7655,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="S2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -7592,7 +7673,7 @@
         <v>1.2</v>
       </c>
       <c r="X2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="Y2" t="b">
         <v>0</v>
@@ -7600,7 +7681,7 @@
     </row>
     <row r="3" spans="1:25">
       <c r="A3" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B3">
         <v>63</v>
@@ -7651,10 +7732,10 @@
         <v>0</v>
       </c>
       <c r="R3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="S3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -7669,7 +7750,7 @@
         <v>1.2</v>
       </c>
       <c r="X3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="Y3" t="b">
         <v>0</v>
